--- a/data/trans_dic/P13A_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,86</t>
+          <t>0,75; 2,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,36</t>
+          <t>0,35; 1,41</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,49</t>
+          <t>1,23; 4,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,98</t>
+          <t>3,6; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,05</t>
+          <t>2,83; 5,19</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,4</t>
+          <t>0,73; 3,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,57</t>
+          <t>3,02; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,59</t>
+          <t>2,23; 4,58</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,94</t>
+          <t>0,18; 1,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,65</t>
+          <t>1,85; 6,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,2</t>
+          <t>1,39; 4,45</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,52</t>
+          <t>1,03; 3,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,99</t>
+          <t>0,8; 3,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,16</t>
+          <t>1,15; 4,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,35</t>
+          <t>3,06; 7,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,99</t>
+          <t>2,39; 4,74</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,6</t>
+          <t>0,54; 2,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,73</t>
+          <t>2,21; 6,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,27</t>
+          <t>2,1; 4,29</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,02</t>
+          <t>2,04; 5,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,63</t>
+          <t>0,82; 2,76</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,5</t>
+          <t>0,73; 1,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,75</t>
+          <t>3,18; 4,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 2,98</t>
+          <t>2,16; 2,98</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses)</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 980</t>
+          <t>0; 858</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1907; 8292</t>
+          <t>2168; 8233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2079; 8193</t>
+          <t>2124; 8455</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6149; 23293</t>
+          <t>6396; 23067</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19092; 35931</t>
+          <t>18559; 35867</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28642; 52195</t>
+          <t>29247; 53593</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2229; 10673</t>
+          <t>2307; 10903</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9873; 22694</t>
+          <t>10441; 23420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14933; 30244</t>
+          <t>14680; 30226</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>577; 6044</t>
+          <t>568; 6147</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9047; 31568</t>
+          <t>8782; 31674</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11485; 33013</t>
+          <t>10938; 34964</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 7914</t>
+          <t>0; 8656</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2153; 7350</t>
+          <t>2158; 8194</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3507; 11597</t>
+          <t>3097; 11635</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3135; 11197</t>
+          <t>3095; 11537</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7968; 18854</t>
+          <t>7866; 17990</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12795; 26269</t>
+          <t>12584; 24950</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3407; 16008</t>
+          <t>3301; 14138</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17991; 56937</t>
+          <t>18646; 56863</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28222; 62465</t>
+          <t>30759; 62749</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5485</t>
+          <t>0; 5548</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14767; 42932</t>
+          <t>14516; 40506</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13725; 43099</t>
+          <t>13520; 45247</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>25102; 51787</t>
+          <t>25203; 51393</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>118711; 173404</t>
+          <t>116137; 172756</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>152673; 211370</t>
+          <t>153163; 211769</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P13A_1_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P13A_1_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,28</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,84</t>
+          <t>0,79; 2,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,41</t>
+          <t>0,46; 1,79</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,45</t>
+          <t>1,24; 4,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 6,96</t>
+          <t>3,58; 6,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,19</t>
+          <t>2,77; 5,13</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,47</t>
+          <t>0,65; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,78</t>
+          <t>3,2; 7,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,58</t>
+          <t>2,47; 4,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,97</t>
+          <t>0,15; 1,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,67</t>
+          <t>2,64; 8,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,45</t>
+          <t>1,64; 4,51</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,93</t>
+          <t>0,97; 3,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,0</t>
+          <t>0,78; 2,69</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,28</t>
+          <t>1,15; 4,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,01</t>
+          <t>2,98; 7,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,74</t>
+          <t>2,43; 5,01</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,29</t>
+          <t>0,54; 2,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,72</t>
+          <t>4,87; 8,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,29</t>
+          <t>3,09; 4,95</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,68</t>
+          <t>1,64; 3,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,76</t>
+          <t>0,88; 2,0</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,49</t>
+          <t>0,83; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,74</t>
+          <t>3,65; 4,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,98</t>
+          <t>2,32; 3,07</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5960</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 858</t>
+          <t>0; 5801</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2168; 8233</t>
+          <t>2484; 9184</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2124; 8455</t>
+          <t>2932; 11360</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26655</t>
+          <t>27650</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>40821</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6396; 23067</t>
+          <t>6580; 23727</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18559; 35867</t>
+          <t>19542; 37574</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29247; 53593</t>
+          <t>29886; 55221</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>17625</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>22890</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2307; 10903</t>
+          <t>2035; 10485</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10441; 23420</t>
+          <t>11304; 25722</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14680; 30226</t>
+          <t>16492; 33033</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>21524</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>568; 6147</t>
+          <t>551; 5253</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8782; 31674</t>
+          <t>11118; 33954</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10938; 34964</t>
+          <t>13040; 35786</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6546</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 8656</t>
+          <t>0; 8745</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2158; 8194</t>
+          <t>2214; 8047</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3097; 11635</t>
+          <t>3386; 11664</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12270</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18495</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3095; 11537</t>
+          <t>3120; 11628</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7866; 17990</t>
+          <t>7837; 18814</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12584; 24950</t>
+          <t>12969; 26759</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>48419</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>57333</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3301; 14138</t>
+          <t>3869; 16410</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18646; 56863</t>
+          <t>37258; 61874</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30759; 62749</t>
+          <t>45580; 73028</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>20275</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>21420</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 5548</t>
+          <t>0; 6442</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14516; 40506</t>
+          <t>13511; 30280</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13520; 45247</t>
+          <t>14249; 32454</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>25203; 51393</t>
+          <t>29269; 55553</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>116137; 172756</t>
+          <t>135676; 179204</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>153163; 211769</t>
+          <t>168200; 222488</t>
         </is>
       </c>
     </row>
